--- a/data/trans_orig/IP24_R2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R2_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21423</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14246</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28744</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13580</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8507</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19492</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16082</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32882</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37540</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48263</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>100829</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93508</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>108006</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>90882</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84970</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>95955</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>112558</t>
+          <t>90144</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>84512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120436</t>
+          <t>94624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>203439</t>
+          <t>190973</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192716</t>
+          <t>181831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213139</t>
+          <t>199769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136518</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10943</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16175</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18071</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12100</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24889</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,2%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>17985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>26065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80037</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84215</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>76045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69227</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82016</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>83084</t>
+          <t>78069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75650</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87390</t>
+          <t>83901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>159129</t>
+          <t>158105</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149573</t>
+          <t>149066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166847</t>
+          <t>165904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6169</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4715</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9192</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>50128</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45849</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52842</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>43489</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37766</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47146</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53895</t>
+          <t>45527</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46583</t>
+          <t>40613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>49347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97384</t>
+          <t>95655</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88665</t>
+          <t>87967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103157</t>
+          <t>100114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38257</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28517</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47798</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>81405</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>55946</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128830</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>125399</t>
+          <t>81504</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97663</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186384</t>
+          <t>95632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161769</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152228</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171509</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135660</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>88235</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,5%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>172084</t>
+          <t>134749</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>160923</t>
+          <t>123698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>182500</t>
+          <t>143308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>307744</t>
+          <t>296518</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246759</t>
+          <t>282390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335480</t>
+          <t>309516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>216078</t>
+          <t>177995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29317</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18548</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52861</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>35,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19238</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13448</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26074</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35811</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41066</t>
+          <t>35052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82708</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>118628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95084</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>129397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>64,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>100190</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93354</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>105980</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126410</t>
+          <t>101165</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100061</t>
+          <t>95034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139032</t>
+          <t>106649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>226601</t>
+          <t>219794</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>198942</t>
+          <t>192625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>240584</t>
+          <t>231624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14731</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12687</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7642</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19893</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,09%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22130</t>
+          <t>19045</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59946</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>53556</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>63649</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>78,43%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>56208</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>49002</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61253</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>81,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>71,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>88,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>59653</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56360</t>
+          <t>54025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>63979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>118768</t>
+          <t>119599</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>111526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125460</t>
+          <t>125046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>114450</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>97321</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>143076</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,69%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>153353</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>124752</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>219731</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>134359</t>
+          <t>110239</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114558</t>
+          <t>95016</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166192</t>
+          <t>126736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>287712</t>
+          <t>224688</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248633</t>
+          <t>199585</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370675</t>
+          <t>251283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>571336</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>542710</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>588465</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>79,14%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>745</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>502474</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>436096</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>531075</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>66,5%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>80,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>610591</t>
+          <t>509307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>578758</t>
+          <t>492810</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630392</t>
+          <t>524530</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1113065</t>
+          <t>1080644</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1030102</t>
+          <t>1054049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1152144</t>
+          <t>1105747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>744950</t>
+          <t>619546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
